--- a/dev/StructureDefinition-bc-license-status-extension.xlsx
+++ b/dev/StructureDefinition-bc-license-status-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1289,7 +1289,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>98</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>113</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>122</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>127</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>129</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>134</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>137</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>142</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>144</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>149</v>
       </c>
@@ -3779,12 +3779,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK28">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
